--- a/Mitarbeiter.xlsx
+++ b/Mitarbeiter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/872c74d94e9acb83/Documents/aktien/TradingAPP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD4DB114E441178AC67DF4497610CAF6693EDF1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97FF76AC-8B39-4E0C-A49F-561D2BE780DB}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_AD4DB114E441178AC67DF4497610CAF6693EDF1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BAA72FA-F3C0-4A7A-B94A-C555672EB303}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Mitarbeiter</t>
   </si>
@@ -121,14 +121,43 @@
   </si>
   <si>
     <t>Depot-Gesamtgewichtung &amp; Risikoverteilung</t>
+  </si>
+  <si>
+    <t>Annemay</t>
+  </si>
+  <si>
+    <t>Psychologin</t>
+  </si>
+  <si>
+    <r>
+      <t>Discipline (Psychologie, Regeldisziplin &amp; Journal-Überprüfung)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -163,7 +192,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -186,21 +215,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -481,10 +528,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="45.75" thickBot="1">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="114.75" thickBot="1">
+    <row r="2" spans="1:4" ht="15.75" thickBot="1">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -512,7 +565,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="129" thickBot="1">
+    <row r="3" spans="1:4" ht="15.75" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -526,7 +579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="129" thickBot="1">
+    <row r="4" spans="1:4" ht="15.75" thickBot="1">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -540,7 +593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="100.5" thickBot="1">
+    <row r="5" spans="1:4" ht="15.75" thickBot="1">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -554,7 +607,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="129" thickBot="1">
+    <row r="6" spans="1:4" ht="15.75" thickBot="1">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -568,7 +621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="114.75" thickBot="1">
+    <row r="7" spans="1:4" ht="15.75" thickBot="1">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -582,7 +635,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="114.75" thickBot="1">
+    <row r="8" spans="1:4" ht="15.75" thickBot="1">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
@@ -594,6 +647,17 @@
       </c>
       <c r="D8" s="2" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
